--- a/artfynd/A 29112-2025 artfynd.xlsx
+++ b/artfynd/A 29112-2025 artfynd.xlsx
@@ -675,43 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126187526</v>
+        <v>126187691</v>
       </c>
       <c r="B2" t="n">
-        <v>58506</v>
+        <v>98341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565564</v>
+        <v>565590</v>
       </c>
       <c r="R2" t="n">
-        <v>6402006</v>
+        <v>6402472</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,7 +784,7 @@
         <v>126187695</v>
       </c>
       <c r="B3" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,42 +887,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126187691</v>
+        <v>126187526</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>58507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>208250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565590</v>
+        <v>565564</v>
       </c>
       <c r="R4" t="n">
-        <v>6402472</v>
+        <v>6402006</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>126187510</v>
       </c>
       <c r="B5" t="n">
-        <v>91651</v>
+        <v>91653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>126187663</v>
       </c>
       <c r="B6" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>126187670</v>
       </c>
       <c r="B7" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29112-2025 artfynd.xlsx
+++ b/artfynd/A 29112-2025 artfynd.xlsx
@@ -675,42 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126187691</v>
+        <v>126187526</v>
       </c>
       <c r="B2" t="n">
-        <v>98341</v>
+        <v>58507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>208250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565590</v>
+        <v>565564</v>
       </c>
       <c r="R2" t="n">
-        <v>6402472</v>
+        <v>6402006</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126187695</v>
+        <v>126187691</v>
       </c>
       <c r="B3" t="n">
-        <v>105365</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126187526</v>
+        <v>126187695</v>
       </c>
       <c r="B4" t="n">
-        <v>58507</v>
+        <v>105365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,32 +899,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565564</v>
+        <v>565590</v>
       </c>
       <c r="R4" t="n">
-        <v>6402006</v>
+        <v>6402472</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 29112-2025 artfynd.xlsx
+++ b/artfynd/A 29112-2025 artfynd.xlsx
@@ -675,43 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126187526</v>
+        <v>126187691</v>
       </c>
       <c r="B2" t="n">
-        <v>58507</v>
+        <v>98343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565564</v>
+        <v>565590</v>
       </c>
       <c r="R2" t="n">
-        <v>6402006</v>
+        <v>6402472</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,42 +781,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126187691</v>
+        <v>126187526</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>58507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>208250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565590</v>
+        <v>565564</v>
       </c>
       <c r="R3" t="n">
-        <v>6402472</v>
+        <v>6402006</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>126187695</v>
       </c>
       <c r="B4" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>126187510</v>
       </c>
       <c r="B5" t="n">
-        <v>91653</v>
+        <v>91655</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>126187663</v>
       </c>
       <c r="B6" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>126187670</v>
       </c>
       <c r="B7" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29112-2025 artfynd.xlsx
+++ b/artfynd/A 29112-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126187691</v>
+        <v>126187695</v>
       </c>
       <c r="B2" t="n">
-        <v>98343</v>
+        <v>105371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -881,39 +881,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126187695</v>
+        <v>126187691</v>
       </c>
       <c r="B4" t="n">
-        <v>105367</v>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -997,7 +997,7 @@
         <v>126187510</v>
       </c>
       <c r="B5" t="n">
-        <v>91655</v>
+        <v>91657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
         <v>126187663</v>
       </c>
       <c r="B6" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>126187670</v>
       </c>
       <c r="B7" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29112-2025 artfynd.xlsx
+++ b/artfynd/A 29112-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126187695</v>
+        <v>126187526</v>
       </c>
       <c r="B2" t="n">
-        <v>105371</v>
+        <v>58511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>208250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565590</v>
+        <v>565564</v>
       </c>
       <c r="R2" t="n">
-        <v>6402472</v>
+        <v>6402006</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126187526</v>
+        <v>126187695</v>
       </c>
       <c r="B3" t="n">
-        <v>58507</v>
+        <v>105384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,32 +793,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208250</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565564</v>
+        <v>565590</v>
       </c>
       <c r="R3" t="n">
-        <v>6402006</v>
+        <v>6402472</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -891,7 +891,7 @@
         <v>126187691</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>126187510</v>
       </c>
       <c r="B5" t="n">
-        <v>91657</v>
+        <v>91661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
         <v>126187663</v>
       </c>
       <c r="B6" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>126187670</v>
       </c>
       <c r="B7" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29112-2025 artfynd.xlsx
+++ b/artfynd/A 29112-2025 artfynd.xlsx
@@ -775,39 +775,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126187695</v>
+        <v>126187691</v>
       </c>
       <c r="B3" t="n">
-        <v>105384</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -888,32 +888,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126187691</v>
+        <v>126187695</v>
       </c>
       <c r="B4" t="n">
-        <v>98349</v>
+        <v>105387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
         <v>126187663</v>
       </c>
       <c r="B6" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>126187670</v>
       </c>
       <c r="B7" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29112-2025 artfynd.xlsx
+++ b/artfynd/A 29112-2025 artfynd.xlsx
@@ -675,43 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126187526</v>
+        <v>126187691</v>
       </c>
       <c r="B2" t="n">
-        <v>58511</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565564</v>
+        <v>565590</v>
       </c>
       <c r="R2" t="n">
-        <v>6402006</v>
+        <v>6402472</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -775,39 +774,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126187691</v>
+        <v>126187695</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>105387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126187695</v>
+        <v>126187526</v>
       </c>
       <c r="B4" t="n">
-        <v>105387</v>
+        <v>58511</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,31 +898,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>208250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565590</v>
+        <v>565564</v>
       </c>
       <c r="R4" t="n">
-        <v>6402472</v>
+        <v>6402006</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 29112-2025 artfynd.xlsx
+++ b/artfynd/A 29112-2025 artfynd.xlsx
@@ -675,42 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126187691</v>
+        <v>126187526</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>58511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>208250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565590</v>
+        <v>565564</v>
       </c>
       <c r="R2" t="n">
-        <v>6402472</v>
+        <v>6402006</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -887,43 +888,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126187526</v>
+        <v>126187691</v>
       </c>
       <c r="B4" t="n">
-        <v>58511</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565564</v>
+        <v>565590</v>
       </c>
       <c r="R4" t="n">
-        <v>6402006</v>
+        <v>6402472</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 29112-2025 artfynd.xlsx
+++ b/artfynd/A 29112-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126187526</v>
       </c>
       <c r="B2" t="n">
-        <v>58511</v>
+        <v>58514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126187695</v>
       </c>
       <c r="B3" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>126187691</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>126187510</v>
       </c>
       <c r="B5" t="n">
-        <v>91661</v>
+        <v>91664</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>126187663</v>
       </c>
       <c r="B6" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>126187670</v>
       </c>
       <c r="B7" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
